--- a/apps/zds/engine/Archive/Grave Placement Archive.xlsx
+++ b/apps/zds/engine/Archive/Grave Placement Archive.xlsx
@@ -12719,7 +12719,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -12887,7 +12887,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13013,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13097,7 +13097,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14147,7 +14147,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14159,27 +14159,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>MRR1</t>
+          <t>Z9SRBuddy</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>Overflow</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14211,12 +14211,12 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>MRR6</t>
+          <t>MRR1</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14253,12 +14253,12 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>MRR7</t>
+          <t>MRR6</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Mike S</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>MRR8</t>
+          <t>MRR7</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14337,12 +14337,12 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Jared</t>
+          <t>Mike S</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>MRR10</t>
+          <t>MRR8</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14379,12 +14379,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Jared</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>WRR1</t>
+          <t>MRR10</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14421,12 +14421,12 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>WRR6</t>
+          <t>WRR1</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Sheri O</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>WRR7</t>
+          <t>WRR6</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Sherry B</t>
+          <t>Sheri O</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>WRR8</t>
+          <t>WRR7</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14547,12 +14547,12 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Sherry B</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>WRR10</t>
+          <t>WRR8</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14589,17 +14589,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Tawnya</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>WRR10</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14631,17 +14631,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Tawnya</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Zone9SR</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Zone-SR</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14673,17 +14673,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Zone1</t>
+          <t>Zone9SR</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Zone-SR</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14715,12 +14715,12 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Kaiden</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Zone4</t>
+          <t>Zone1</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14757,12 +14757,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Robby</t>
+          <t>Kaiden</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Zone5</t>
+          <t>Zone4</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14799,12 +14799,12 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Robby</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Zone8</t>
+          <t>Zone5</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14841,12 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Zone10</t>
+          <t>Zone8</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14883,12 +14883,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Zone3</t>
+          <t>Zone10</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14925,12 +14925,12 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Gary</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Zone2</t>
+          <t>Zone3</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -14967,12 +14967,12 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Gary</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Zone7</t>
+          <t>Zone2</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15009,12 +15009,12 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Zone6</t>
+          <t>Zone7</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15051,12 +15051,12 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Mike W</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Zone9</t>
+          <t>Zone6</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15093,17 +15093,17 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Mike W</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Trash1</t>
+          <t>Zone9</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Trash</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15135,17 +15135,17 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>MP1</t>
+          <t>Trash1</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Trash</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15177,27 +15177,27 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Alistair</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>PMOL1</t>
+          <t>MP1</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>PM-OL</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>pm_ol</t>
+          <t>grave</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15219,12 +15219,12 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Alistair</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>PMOL2</t>
+          <t>PMOL1</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15261,12 +15261,12 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>PMOL3</t>
+          <t>PMOL2</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15303,12 +15303,12 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Missy</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>PMOL4</t>
+          <t>PMOL3</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15345,27 +15345,27 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Char</t>
+          <t>Missy</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AMOL1</t>
+          <t>PMOL4</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>AM-OL</t>
+          <t>PM-OL</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>am_ol</t>
+          <t>pm_ol</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15387,12 +15387,12 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Char</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AMOL2</t>
+          <t>AMOL1</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AMOL3</t>
+          <t>AMOL2</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15471,12 +15471,12 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LeeAnn</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AMOL4</t>
+          <t>AMOL3</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15513,12 +15513,12 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>LeeAnn</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AMOL5</t>
+          <t>AMOL4</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15555,12 +15555,12 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AMOL6</t>
+          <t>AMOL5</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15587,37 +15587,37 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Jared</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>MRR1</t>
+          <t>AMOL6</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>AM-OL</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>grave</t>
+          <t>am_ol</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15629,27 +15629,27 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Kaiden</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>MRR6</t>
+          <t>Z9SRBuddy</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>Overflow</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15681,12 +15681,12 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Jared</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>MRR7</t>
+          <t>MRR1</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15723,12 +15723,12 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Kaiden</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>MRR8</t>
+          <t>MRR6</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15765,12 +15765,12 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Mike S</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>MRR10</t>
+          <t>MRR7</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15807,12 +15807,12 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>WRR1</t>
+          <t>MRR8</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15849,12 +15849,12 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Tawnya</t>
+          <t>Mike S</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>WRR6</t>
+          <t>MRR10</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15891,12 +15891,12 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>WRR7</t>
+          <t>WRR1</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15933,12 +15933,12 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Sheri O</t>
+          <t>Tawnya</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>WRR8</t>
+          <t>WRR6</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -15975,12 +15975,12 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Sherry B</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>WRR10</t>
+          <t>WRR7</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16017,17 +16017,17 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Sheri O</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Zone9SR</t>
+          <t>WRR8</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Zone-SR</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16059,17 +16059,17 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Darlene</t>
+          <t>Sherry B</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Zone1</t>
+          <t>WRR10</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16101,17 +16101,17 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Zone4</t>
+          <t>Zone9SR</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Zone-SR</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16143,12 +16143,12 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Darlene</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Zone5</t>
+          <t>Zone1</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16185,12 +16185,12 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Zone8</t>
+          <t>Zone4</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16227,12 +16227,12 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Cookie</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Zone10</t>
+          <t>Zone5</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16269,12 +16269,12 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Zone3</t>
+          <t>Zone8</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16311,12 +16311,12 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Cookie</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Zone2</t>
+          <t>Zone10</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16353,12 +16353,12 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Mike W</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Zone7</t>
+          <t>Zone3</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16395,12 +16395,12 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Zone6</t>
+          <t>Zone2</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16437,12 +16437,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Mike W</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Zone9</t>
+          <t>Zone7</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16479,27 +16479,27 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>PMOL1</t>
+          <t>Zone6</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>PM-OL</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>pm_ol</t>
+          <t>grave</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16521,27 +16521,27 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>PMOL2</t>
+          <t>Zone9</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>PM-OL</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>pm_ol</t>
+          <t>grave</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16563,12 +16563,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Missy</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>PMOL3</t>
+          <t>PMOL1</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16605,12 +16605,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Becca</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>PMOL4</t>
+          <t>PMOL2</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16647,27 +16647,27 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Auggie</t>
+          <t>Missy</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AMOL1</t>
+          <t>PMOL3</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>AM-OL</t>
+          <t>PM-OL</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>am_ol</t>
+          <t>pm_ol</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16689,27 +16689,27 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Char</t>
+          <t>Becca</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AMOL2</t>
+          <t>PMOL4</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>AM-OL</t>
+          <t>PM-OL</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>am_ol</t>
+          <t>pm_ol</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16731,12 +16731,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Auggie</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AMOL3</t>
+          <t>AMOL1</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16773,12 +16773,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>LeeAnn</t>
+          <t>Char</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AMOL4</t>
+          <t>AMOL2</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16815,27 +16815,27 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Support3</t>
+          <t>AMOL3</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Overflow</t>
+          <t>AM-OL</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>grave</t>
+          <t>am_ol</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16847,37 +16847,37 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>LeeAnn</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>MRR1</t>
+          <t>AMOL4</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>AM-OL</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>grave</t>
+          <t>am_ol</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16889,27 +16889,27 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>MRR6</t>
+          <t>Support3</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>Overflow</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16941,12 +16941,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Daryl</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>MRR7</t>
+          <t>MRR1</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -16983,12 +16983,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Jared</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>MRR8</t>
+          <t>MRR6</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17025,12 +17025,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Daryl</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>MRR10</t>
+          <t>MRR7</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17067,12 +17067,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Jared</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>WRR1</t>
+          <t>MRR8</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17109,12 +17109,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>WRR6</t>
+          <t>MRR10</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Sherry B</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>WRR7</t>
+          <t>WRR1</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17193,12 +17193,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>WRR8</t>
+          <t>WRR6</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17235,12 +17235,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Sherry B</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>WRR10</t>
+          <t>WRR7</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17277,17 +17277,17 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Sheri O</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>WRR8</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17319,17 +17319,17 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Zone9SR</t>
+          <t>WRR10</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Zone-SR</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -17339,7 +17339,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17361,17 +17361,17 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Sheri O</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Zone1</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17403,17 +17403,17 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Darlene</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Zone4</t>
+          <t>Zone9SR</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Zone-SR</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17445,12 +17445,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Cookie</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Zone5</t>
+          <t>Zone1</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17487,12 +17487,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Kaylee</t>
+          <t>Darlene</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Zone8</t>
+          <t>Zone4</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17529,12 +17529,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Cookie</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Zone10</t>
+          <t>Zone5</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17571,27 +17571,27 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Kaylee</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>PMOL1</t>
+          <t>Zone8</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>PM-OL</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>pm_ol</t>
+          <t>grave</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17613,27 +17613,27 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>PMOL2</t>
+          <t>Zone10</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>PM-OL</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>pm_ol</t>
+          <t>grave</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17655,12 +17655,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Becca</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>PMOL3</t>
+          <t>PMOL1</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17697,27 +17697,27 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Auggie</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>AMOL1</t>
+          <t>PMOL2</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>AM-OL</t>
+          <t>PM-OL</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>am_ol</t>
+          <t>pm_ol</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17739,27 +17739,27 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Becca</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>AMOL2</t>
+          <t>PMOL3</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>AM-OL</t>
+          <t>PM-OL</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>am_ol</t>
+          <t>pm_ol</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17781,12 +17781,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>LeeAnn</t>
+          <t>Auggie</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>AMOL3</t>
+          <t>AMOL1</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17823,27 +17823,27 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Support3</t>
+          <t>AMOL2</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Overflow</t>
+          <t>AM-OL</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>grave</t>
+          <t>am_ol</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17855,37 +17855,37 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>LeeAnn</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>MRR1</t>
+          <t>AMOL3</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>AM-OL</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>grave</t>
+          <t>am_ol</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17897,27 +17897,27 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>MRR6</t>
+          <t>Support3</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Restroom</t>
+          <t>Overflow</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -17927,7 +17927,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17949,12 +17949,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>MRR7</t>
+          <t>MRR1</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Daryl</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>MRR8</t>
+          <t>MRR6</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18033,12 +18033,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Alec</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>MRR10</t>
+          <t>MRR7</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18075,12 +18075,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Daryl</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>WRR1</t>
+          <t>MRR8</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18117,12 +18117,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Alec</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>WRR6</t>
+          <t>MRR10</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18159,12 +18159,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Kaylee</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>WRR7</t>
+          <t>WRR1</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18201,12 +18201,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>WRR8</t>
+          <t>WRR6</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18243,12 +18243,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Sheri O</t>
+          <t>Kaylee</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>WRR10</t>
+          <t>WRR7</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18285,17 +18285,17 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>WRR8</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18327,17 +18327,17 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Sheri O</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Zone9SR</t>
+          <t>WRR10</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Zone-SR</t>
+          <t>Restroom</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18369,17 +18369,17 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Cookie</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Zone1</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18416,12 +18416,12 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Zone4</t>
+          <t>Zone9SR</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Zone-SR</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18453,12 +18453,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Darlene</t>
+          <t>Cookie</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Zone5</t>
+          <t>Zone1</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Zone8</t>
+          <t>Zone4</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18537,12 +18537,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Darlene</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Zone10</t>
+          <t>Zone5</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18579,27 +18579,27 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>PMOL1</t>
+          <t>Zone8</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>PM-OL</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>pm_ol</t>
+          <t>grave</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18621,12 +18621,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>PMOL2</t>
+          <t>PMOL1</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18663,12 +18663,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Polly</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>PMOL3</t>
+          <t>PMOL2</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18705,27 +18705,27 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Auggie</t>
+          <t>Polly</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>AMOL1</t>
+          <t>PMOL3</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>AM-OL</t>
+          <t>PM-OL</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>am_ol</t>
+          <t>pm_ol</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18747,12 +18747,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Auggie</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>AMOL2</t>
+          <t>AMOL1</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18789,12 +18789,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>LeeAnn</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>AMOL3</t>
+          <t>AMOL2</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18831,27 +18831,27 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>LeeAnn</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Support3</t>
+          <t>AMOL3</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Overflow</t>
+          <t>AM-OL</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>grave</t>
+          <t>am_ol</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19019,7 +19019,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Cookie</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Cookie</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19439,7 +19439,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19481,7 +19481,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19733,7 +19733,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20027,7 +20027,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20573,7 +20573,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20699,7 +20699,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20783,7 +20783,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>2026-05-03T06:51:38</t>
+          <t>2026-05-06T07:24:54</t>
         </is>
       </c>
     </row>
@@ -20798,7 +20798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21412,11 +21412,7 @@
           <t>1x (last 2026-04-23)</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
@@ -21424,7 +21420,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -21532,12 +21528,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3x (last 2026-05-06)</t>
+          <t>2x (last 2026-04-29)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-28)</t>
+          <t>2x (last 2026-05-06)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -21848,7 +21844,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -21873,24 +21869,28 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4x (last 2026-05-07)</t>
+          <t>1x (last 2026-05-03)</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -21920,82 +21920,42 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-07)</t>
+        </is>
+      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gary</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-06)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-07)</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-29)</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-23)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-30)</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -22004,39 +21964,35 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Gary</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-01)</t>
+          <t>1x (last 2026-05-06)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-06)</t>
+          <t>1x (last 2026-04-22)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-07)</t>
+          <t>1x (last 2026-04-29)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -22044,20 +22000,44 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-23)</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-30)</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -22066,39 +22046,39 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2x (last 2026-05-04)</t>
+          <t>1x (last 2026-05-01)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4x (last 2026-04-30)</t>
+          <t>1x (last 2026-05-02)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-27)</t>
+          <t>1x (last 2026-05-05)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>1x (last 2026-05-06)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>1x (last 2026-05-07)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-23)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -22107,32 +22087,20 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
@@ -22140,67 +22108,71 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jamie</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5x (last 2026-05-05)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-04)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4x (last 2026-04-30)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>1x (last 2026-04-27)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-21)</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>1x (last 2026-04-20)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-04)</t>
+          <t>1x (last 2026-05-03)</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -22210,65 +22182,69 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jared</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
+          <t>Jamie</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
         <is>
           <t>1x (last 2026-05-03)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>1x (last 2026-04-27)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>1x (last 2026-04-20)</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -22276,35 +22252,39 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Jared</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-05)</t>
+          <t>1x (last 2026-04-27)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-23)</t>
+          <t>2x (last 2026-04-26)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-20)</t>
+          <t>3x (last 2026-05-04)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-21)</t>
+          <t>1x (last 2026-05-02)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -22313,35 +22293,23 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-29)</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2x (last 2026-05-06)</t>
+          <t>1x (last 2026-05-01)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-07)</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
@@ -22350,31 +22318,35 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-07)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-23)</t>
+          <t>1x (last 2026-04-20)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-26)</t>
+          <t>1x (last 2026-04-21)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -22382,48 +22354,36 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-29)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>1x (last 2026-04-22)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
         <is>
           <t>2x (last 2026-05-06)</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-29)</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-07)</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -22438,97 +22398,89 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>1x (last 2026-05-03)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-06)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>1x (last 2026-05-02)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-21)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-27)</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-29)</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -22537,100 +22489,124 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>1x (last 2026-05-02)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-28)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>1x (last 2026-04-24)</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kaiden</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -22642,72 +22618,64 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Kaiden</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-06)</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-27)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-05)</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-29)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -22716,20 +22684,16 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kaylee</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-27)</t>
-        </is>
-      </c>
+          <t>Kathy</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -22739,50 +22703,62 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-06)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-28)</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
           <t>1x (last 2026-05-05)</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>1x (last 2026-04-20)</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-03)</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
           <t>2x (last 2026-04-29)</t>
         </is>
       </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
@@ -22790,16 +22766,20 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LeeAnn</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>Kaylee</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-27)</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -22807,20 +22787,52 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-28)</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-29)</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
@@ -22828,13 +22840,13 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Liz</t>
+          <t>LeeAnn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -22844,48 +22856,20 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-23)</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-21)</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-29)</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -22894,13 +22878,13 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Liz</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -22910,44 +22894,48 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-27)</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>1x (last 2026-04-29)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-21)</t>
+          <t>1x (last 2026-04-28)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-03)</t>
+          <t>1x (last 2026-04-25)</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -22962,7 +22950,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -22971,58 +22959,46 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-28)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-27)</t>
+          <t>1x (last 2026-04-20)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>1x (last 2026-04-21)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>1x (last 2026-05-03)</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
@@ -23030,13 +23006,13 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -23045,22 +23021,58 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-28)</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
@@ -23068,62 +23080,34 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mike S</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3x (last 2026-04-30)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-03)</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-07)</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-23)</t>
-        </is>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
@@ -23134,35 +23118,39 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mike W</t>
+          <t>Mike S</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3x (last 2026-04-30)</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-23)</t>
+          <t>1x (last 2026-04-25)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-06)</t>
+          <t>1x (last 2026-05-01)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-29)</t>
+          <t>1x (last 2026-05-02)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-30)</t>
+          <t>2x (last 2026-05-03)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -23170,71 +23158,63 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-07)</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Missy</t>
+          <t>Mike W</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-06)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-29)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-30)</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -23243,28 +23223,60 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Missy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -23274,69 +23286,21 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-21)</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-28)</t>
-        </is>
-      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-27)</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
@@ -23344,73 +23308,105 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>1x (last 2026-05-01)</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-28)</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-05)</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Polly</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -23419,327 +23415,303 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Robby</t>
+          <t>Polly</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-06)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-07)</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-30)</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-23)</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-24)</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-25)</t>
-        </is>
-      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sam</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3x (last 2026-05-07)</t>
-        </is>
-      </c>
+          <t>Robby</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-06)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>3x (last 2026-05-06)</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-04)</t>
+          <t>1x (last 2026-04-30)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-23)</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-27)</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-24)</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-25)</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-21)</t>
+          <t>1x (last 2026-05-01)</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Seth</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-20)</t>
-        </is>
-      </c>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3x (last 2026-05-07)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-28)</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-30)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-06)</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-27)</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-28)</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>3x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sheri O</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Seth</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-28)</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>3x (last 2026-04-29)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-05)</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-27)</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-21)</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-06)</t>
-        </is>
-      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>3x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sherry B</t>
+          <t>Sheri O</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-20)</t>
+          <t>2x (last 2026-05-04)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -23749,44 +23721,52 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-26)</t>
+          <t>3x (last 2026-04-29)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2x (last 2026-04-27)</t>
+          <t>2x (last 2026-04-28)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2x (last 2026-05-04)</t>
+          <t>1x (last 2026-05-02)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-02)</t>
+          <t>1x (last 2026-05-03)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-03)</t>
+          <t>2x (last 2026-05-05)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-21)</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-06)</t>
+        </is>
+      </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
@@ -23794,16 +23774,20 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Silvia</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>Sherry B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-20)</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -23811,60 +23795,44 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-06)</t>
+          <t>1x (last 2026-04-26)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-07)</t>
+          <t>2x (last 2026-04-27)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-29)</t>
+          <t>2x (last 2026-05-04)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2x (last 2026-04-30)</t>
+          <t>1x (last 2026-05-02)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-23)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-22)</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>3x (last 2026-05-02)</t>
-        </is>
-      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
@@ -23872,73 +23840,77 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-05)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-04)</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>3x (last 2026-04-28)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-26)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-27)</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-06)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-07)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-29)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-30)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1x (last 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-19)</t>
-        </is>
-      </c>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-22)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>3x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
@@ -23952,58 +23924,66 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tawnya</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-02)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-04)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3x (last 2026-04-28)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-26)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-27)</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>1x (last 2026-05-03)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2x (last 2026-04-30)</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>1x (last 2026-05-01)</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2x (last 2026-05-07)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1x (last 2026-04-23)</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
+          <t>1x (last 2026-05-02)</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-19)</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1x (last 2026-04-26)</t>
-        </is>
-      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -24012,34 +23992,62 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tiffany</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>Tawnya</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-02)</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2x (last 2026-04-30)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1x (last 2026-05-01)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2x (last 2026-05-07)</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-23)</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1x (last 2026-04-26)</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
@@ -24050,13 +24058,13 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Trenidee</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -24084,14 +24092,52 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>4x (last 2026-04-30)</t>
-        </is>
-      </c>
+      <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Trenidee</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>4x (last 2026-04-30)</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="n">
         <v>4</v>
       </c>
     </row>
